--- a/data/daily/2026-09/2026-09-15.xlsx
+++ b/data/daily/2026-09/2026-09-15.xlsx
@@ -1170,14 +1170,64 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,67 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="323850" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1342,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>8</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1367,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="381000" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="361950" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,27 +1425,77 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1453,49 +1503,99 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="866775" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1503,24 +1603,24 @@
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1528,129 +1628,29 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1028700" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="990600" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,21 +2596,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16045</v>
+        <v>16046</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 시 실제로 힘이 나고 피로 회복에 큰 도움이 됨</t>
+          <t>선물용 높은 만족도 — 생일이나 응원 선물로 주고받기 유용한 구성임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>부담 없는 맛과 제형 — 맛이 좋고 몸에 잘 받아 매일 부담 없이 섭취 가능함</t>
+          <t>우수한 피로 회복 — 힘이 없을 때 섭취 시 체력 보충과 피로 회복에 도움 됨</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>선물용에 적합한 구성 — 생일이나 응원 선물로 주거나 받기에 부담이 없고 만족스러움</t>
+          <t>좋은 맛과 높은 흡수 — 비타민 맛이 좋고 몸에 잘 받아 섭취하기 편함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,26 +2655,26 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15381</v>
+        <v>15382</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 네이비와 오렌지 컬러의 세련된 포장에 휴대하기 좋은 작은 용기로 구성됨</t>
+          <t>고급스러운 패키지 — 네이비와 오렌지 컬러로 깔끔하며 휴대용 용기가 편리함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>상큼하고 달콤한 맛 — 텁텁함이나 부담스러운 맛 없이 상큼한 복숭아 맛으로 맛있게 먹기 좋음</t>
+          <t>편리한 섭취와 달콤함 — 한 번에 섭취하기 쉽고 너무 시지 않아 달콤함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>체력 보충 및 활력 증진 — 야근이나 피로 시 섭취하면 축 처진 느낌이 줄고 정신이 번쩍 듦</t>
+          <t>체력 보충 효과 — 야근이나 피곤할 때 섭취하면 피로 회복에 도움 됨</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 관련 불편 발생 — 배송 기사 연락 문제나 구매 확정 오류 등으로 상품을 미수령하는 상황이 생김</t>
+          <t>배송 미수령 문제 — 구매 결정 과정 중 상품을 실제로 전달받지 못함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -2722,17 +2722,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>빠른 피로 해소 — 지속된 피로와 지친 체력을 풀어주고 몸에 힘을 북돋아 줌</t>
+          <t>피로 개선 효과 — 섭취 후 피로가 풀리고 컨디션 회복에 도움 됨</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 포장 상태 — 포장이 고급스러워 선물용이나 본인 케어용으로 기분 좋게 수령함</t>
+          <t>정성스러운 포장 — 고급스럽게 포장되어 선물용으로 전달하기 양호함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>좋은 맛과 높은 만족도 — 비타민 맛이 좋고 부담이 없어 꾸준히 챙겨 먹기 좋음</t>
+          <t>맛있는 비타민 — 비타민 맛이 우수하여 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2781,17 +2781,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>간편한 올인원 복용 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취 가능함</t>
+          <t>간편한 올인원 복용 — 여러 영양제 대신 한 번에 챙길 수 있어 간편함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>알찬 단독 증정 구성 — 카카오 선물하기 전용 구성으로 추가 증정분이 포함되어 실용적임</t>
+          <t>빠른 피로 회복 — 피로 회복 및 몸의 생기 회복에 도움 됨</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>컨디션 회복 체감 — 피로감이 줄어들고 컨디션 및 생기 회복에 도움을 줌</t>
+          <t>알찬 증정 구성 — 선물하기 전용 추가 증정 구성이 포함되어 실용적임</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2836,29 +2836,29 @@
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>6459</v>
+        <v>6460</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 알약 거부감 없이 과일 향의 맛있는 구미 형태로 간식처럼 먹을 수 있음</t>
+          <t>구미 제형의 편의성 — 알약 대신 젤리 형태라 부담 없이 자주 챙겨 먹게 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>쉽고 재미있는 섭취 — 물 없이 하루 2알씩 챙겨 먹기 쉬워 아이와 어른 모두 잘 챙겨 먹게 됨</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>상큼한 과일 맛 — 새콤달콤한 과일 향으로 맛이 좋아 아이들도 잘 먹음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>꼼꼼한 배송 포장 — 배송 시 포장이 매우 꼼꼼하게 도착함</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>미미한 효과 체감 — 맛있게 먹을 수 있으나 섭취 후 즉각적인 영양 효과 체감은 명확하지 않음</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>약간의 씁쓸한 뒷맛 — 달지 않은 편이며 사람에 따라 약간 씁쓸한 맛이 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>맛에 대한 호불호 — 달지 않고 약간 씁쓸한 느낌이 남아 호불호가 갈림</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
@@ -2903,17 +2903,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물용 패키지가 깔끔하고 예뻐서 주고받을 때 감동을 줌</t>
+          <t>쉬운 알약 목넘김 — 알약 크기가 작아 액상과 함께 삼키기 용이함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>목넘김 편한 알약 크기 — 함께 들어있는 알약 크기가 크지 않아 수월하게 삼킬 수 있음</t>
+          <t>확실한 컨디션 회복 — 체력이 떨어졌을 때 섭취 시 컨디션 회복에 도움 됨</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>확실한 컨디션 회복 — 육아나 일상으로 지친 체력을 빠르게 회복시키는 데에 효과적임</t>
+          <t>이쁜 선물 포장 — 선물 포장 패키지가 고급스럽고 이쁘게 구성됨</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2962,17 +2962,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>우수한 컨디션 회복력 — 피로도가 높거나 감기 등 몸이 안 좋을 때 복용 시 빠른 회복에 도움 됨</t>
+          <t>탁월한 피로 회복 — 복용 후 피로감 감소 및 컨디션 회복에 탁월함</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>편리한 휴대성 및 복용법 — 가지고 다니기 용이하고 마시기 편한 제형으로 섭취가 간편함</t>
+          <t>우수한 휴대성 — 가지고 다니기 좋고 간편하게 마시기 편함</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>뛰어난 맛과 배송 만족 — 맛이 좋아 부담이 없으며 배송이 빠르고 선물용으로 유용함</t>
+          <t>신속한 배송 서비스 — 주문 후 배송 처리가 신속하여 만족스러움</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3017,21 +3017,21 @@
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 용기와 포장이 버리기 아까울 정도로 깔끔하여 선물용으로 제격임</t>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드로 품질에 대한 믿음이 감</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>쓴맛 없는 달콤새콤한 맛 — 홍삼 원료임에도 불구하고 쓴맛이 적고 새콤달콤해서 먹기 편함</t>
+          <t>고급스러운 디자인 — 패키지와 병 디자인이 고급스러워 선물용으로 적합함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>뛰어난 휴대성 — 가방이나 주머니에 간편히 소지하며 챙겨 먹기 적합함</t>
+          <t>부담 없는 맛 — 쓴맛이 적고 달콤새콤하여 아침저녁으로 먹기 편함</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3080,17 +3080,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>개운한 피로 개선 — 피로감이 덜하고 섭취 후 하루를 개운하게 보낼 수 있음</t>
+          <t>고급스러운 패키지 — 패키지 디자인이 고급스럽고 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>고급스러운 구성 — 선물 패키지가 깔끔하고 증정품 젤리가 포함되어 받으면 기분이 좋음</t>
+          <t>피로 개선 체감 — 섭취 시 개운하고 피로감이 덜 느껴짐</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>맛과 빠른 배송 — 맛이 좋아 먹기 부담 없으며 배송이 빨라 만족스러움</t>
+          <t>신속한 배송 — 배송이 빠르게 도착하여 이용하기 편함</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3139,18 +3139,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>지속되는 활력 유지 — 꾸준히 먹으면 피로함이 덜하고 쌩쌩한 상태가 오래 유지됨</t>
+          <t>뛰어난 휴대성 — 하루 하나씩 가지고 다니며 먹기 편리함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>우수한 휴대성과 포장 — 하루 한 개씩 들고 다니기 편하며 성의 있는 정성스러운 포장임</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>지속적인 피로 개선 — 꾸준히 섭취 시 피로함이 덜하고 컨디션 유지에 도움 됨</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>만족스러운 포장 — 선물 포장 디자인이 깔끔하고 성의 있게 느껴짐</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품에 비해 알약 크기가 커서 삼키기가 다소 힘들 수 있음</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
@@ -3194,24 +3198,24 @@
         <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>과하지 않고 맛있는 풍미 — 달지 않으며 포째 먹거나 물에 타 먹기 좋아 계속 손이 가는 맛임</t>
+          <t>부담 없는 맛 — 많이 달지 않고 맛있어서 그냥 먹거나 물에 타 먹기 편함</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>풍성한 사은품 혜택 — 포토카드 등 추가 사은품과 예쁜 포장이 제공되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>탄산수 혼합 시 거품 발생 — 탄산수에 타서 마실 경우 거품이 일어 넘칠 위험이 있어 주의 필요함</t>
-        </is>
-      </c>
+          <t>알찬 증정 구성 — 혜자로운 사은품과 포토카드 구성으로 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>간편한 장 건강 케어 — 맛있고 먹기 편해 일상에서 장 건강 챙기기 용이함</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 +파로저당단백칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 증정</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3246,7 +3250,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260914173414_1a57c7b2225347c68ce00a747f0548ed.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260915132146_bf977745343b4bb485cda5b48cdc1dd2.jpg</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -3257,17 +3261,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>식후 더부룩함 해소 — 고기나 밀가루 섭취 후 복용 시 속의 답답함과 더부룩함이 편안해짐</t>
+          <t>소화 개선 효과 — 식후 속 더부룩함이나 답답한 느낌을 줄여줌</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>배변 활동에 도움 — 꾸준히 섭취하면 배변 활동이 원활해지고 속이 개운해짐</t>
+          <t>고소한 군고구마 맛 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 군고구마 풍미가 느껴지는 고소한 맛으로 부담 없이 즐기기 좋음</t>
+          <t>합리적인 가격 — 할인 행사가 자주 진행되어 가성비 있게 구매 가능함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3285,7 +3289,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[라이브 선착순 혜택] "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+앰플 3입 증정</t>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3316,17 +3320,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 은은한 핑크 빛 포장이 매우 고급스럽고 정성스러워 선물하기에 좋음</t>
+          <t>고급스러운 포장 연출 — 포장이 매우 정성스럽고 예뻐 선물 받는 느낌이 좋음</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>피부 상태 개선 체감 — 꾸준히 마시면 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
+          <t>피부 상태 개선 체감 — 섭취 후 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>간편한 용기와 샘플 구성 — 먹기 편리한 용기 구조에 샘플까지 포함되어 이용이 간편함</t>
+          <t>편리한 섭취 및 샘플 — 먹기 편한 액상 형태이며 샘플 증정이 포함됨</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -3344,7 +3348,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3375,25 +3379,25 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>저렴한 특가 및 증정 혜택 — 추가 증정 10포와 사은품 구성으로 합리적인 가격에 구매 가능함</t>
+          <t>저렴한 특가 구매 — 행사 및 추가 증정 포함 저렴한 가격에 구매 가능함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>고급스러운 포장과 맛 — 포장이 고급지고 맛도 거부감이 없어 매일 복용하기 적합함</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
+          <t>고급스러운 패키지 — 포장이 고급스럽게 와서 선물용으로 적합함</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>무난한 섭취감 — 먹기 편하고 맛도 나쁘지 않아 꾸준히 먹기 좋음</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>초기 장 반응 발생 — 복용 초기 뱃속이 꾸르륵거리거나 가스가 차는 현상이 발생할 수 있음</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>미배송 문제 발생 — 주문 후 상품을 배송받지 못했다는 불만이 존재함</t>
-        </is>
-      </c>
+          <t>배송 미수령 이슈 — 주문 후 제품을 전달받지 못했다는 의견이 있음</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3438,22 +3442,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>부드럽고 다양한 맛 — 퍽퍽하지 않고 부드러우며 소스 종류가 많아 질리지 않고 먹기 좋음</t>
+          <t>부드러운 닭가슴살 식감 — 뻑뻑하지 않고 부드러워 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 패키지 — 많은 수량의 닭가슴살을 부담 없는 저렴한 가격으로 구매 가능함</t>
+          <t>다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 질리지 않음</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>간편한 조리 방식 — 전자레인지로 쉽게 조리할 수 있어 다이어트 식단으로 편함</t>
+          <t>뛰어난 가성비 — 저렴한 가격에 많은 양을 구매할 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아 도착함</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3501,17 +3505,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함이나 비린 맛이 없이 달콤하고 깔끔함</t>
+          <t>텁텁함 없는 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함이 거의 없음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>속 편한 저당 음료 — 당과 칼로리가 낮고 복용 후 속 더부룩함이 적어 운동 전후에 적합함</t>
+          <t>든든한 포만감 — 운동 후나 허기질 때 간식 대용으로 포만감을 줌</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>우수한 포만감과 휴대성 — 슬림한 팩 형태로 휴대가 용이하며 허기를 채워주는 포만감이 있음</t>
+          <t>부드러운 목넘김 — 목넘김이 부드럽고 속이 더부룩하지 않아 편안함</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3560,25 +3564,25 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>다양한 구성과 맛 — 골라 먹는 재미가 있고 간편식 및 점심 식단으로 활용하기 좋음</t>
+          <t>우수한 가성비 — 저렴한 가격에 알찬 식단 구성으로 구매 가능함</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>합리적인 세트 가격 — 넉넉한 개수와 증정 보냉백을 포함한 패키지 가격이 가성비가 좋음</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
+          <t>골라 먹는 재미 — 종류가 다양하여 매일 다채롭게 선택해 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>사은품 보냉백 증정 — 보냉 파우치가 함께 증정되어 도시락용으로 유용함</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>배송 시 상품 해동 — 상품 수령 시 냉동 상태가 유지되지 못하고 녹아서 옴</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>증정품 크기 차이 — 함께 제공되는 사은품 보냉백이 생각보다 다소 크게 느껴질 수 있음</t>
-        </is>
-      </c>
+          <t>제품 해동 상태 — 배송 시 제품이 많이 녹아 도착하는 경우가 있음</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
     </row>
     <row r="19" ht="38" customHeight="1">
@@ -3623,15 +3627,19 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 부담 없는 레몬맛 액상 타입으로 물에 타서 외출 시 먹기 편리함</t>
+          <t>상큼한 레몬맛 — 레몬맛 액상 형태라 부담 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>일상 및 운동 활력 증진 — 공복 복용 시 피로 회복과 운동 수행에 도움을 얻을 수 있음</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
+          <t>편리한 휴대성 — 스틱 제형이라 외출 시 챙겨 다니기 편리함</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>에너지 충전 체감 — 공복이나 운동 전 섭취 시 체력 보충과 활력에 도움 됨</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -3647,7 +3655,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3657,38 +3665,38 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>43,900원</t>
+          <t>25,900원</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7417420</t>
+          <t>https://gift.kakao.com/product/7556791</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
         </is>
       </c>
       <c r="I20" t="n">
         <v>4</v>
       </c>
       <c r="J20" t="n">
-        <v>248</v>
+        <v>1533</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 — 고함량 아르기닌 함유로 피로 해소와 운동 수행 능력에 효과적임</t>
+          <t>실속 있는 영양 조합 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 알참</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>선물용 고급 패키지 — 전용 쇼핑백과 추가 포 증정 구성이 잘 갖추어져 선물로 매우 좋음</t>
+          <t>피로 개선 효과 — 아침에 일어날 때 몸이 덜 무겁고 활력이 생김</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>간편한 개별 포장 — 1포씩 개별 포장되어 있어 가지고 다니며 하루 1포 챙기기 용이함</t>
+          <t>증정 쇼핑백 제공 — 쇼핑백이 함께 포함되어 선물용으로 깔끔함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3706,7 +3714,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3716,38 +3724,38 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>43,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/7417420</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260706153340_3e124da6e254462d9a7efad2521e3b9e.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1533</v>
+        <v>248</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있어 건강 관리에 효율적임</t>
+          <t>고함량 성분 구성 — 1포당 6,200mg 고함량 아르기닌으로 활력 충전에 도움 됨</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>확실한 체력 및 피로 개선 — 아침 복용 시 몸이 한결 가볍고 운동 중 활력 유지가 잘 됨</t>
+          <t>간편한 섭취 및 휴대 — 개별 포장되어 원할 때 하나씩 꺼내 먹기 용이함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>쇼핑백 포함 선물용 제격 — 고급스러운 쇼핑백이 같이 배송되어 선물 전달용으로도 깔끔함</t>
+          <t>고급스러운 포장 — 전용 쇼핑백과 깔끔한 디자인으로 선물하기 좋음</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -4072,10 +4080,10 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16045</v>
+        <v>16046</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15381</v>
+        <v>15382</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>3348</v>
@@ -4084,7 +4092,7 @@
         <v>8703</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>6459</v>
+        <v>6460</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>782</v>
@@ -4093,7 +4101,7 @@
         <v>734</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>2616</v>
@@ -4110,74 +4118,76 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 시 실제로 힘이 나고 피로 회복에 큰 도움이 됨
-부담 없는 맛과 제형 — 맛이 좋고 몸에 잘 받아 매일 부담 없이 섭취 가능함
-선물용에 적합한 구성 — 생일이나 응원 선물로 주거나 받기에 부담이 없고 만족스러움</t>
+          <t>선물용 높은 만족도 — 생일이나 응원 선물로 주고받기 유용한 구성임
+우수한 피로 회복 — 힘이 없을 때 섭취 시 체력 보충과 피로 회복에 도움 됨
+좋은 맛과 높은 흡수 — 비타민 맛이 좋고 몸에 잘 받아 섭취하기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 디자인 — 네이비와 오렌지 컬러의 세련된 포장에 휴대하기 좋은 작은 용기로 구성됨
-상큼하고 달콤한 맛 — 텁텁함이나 부담스러운 맛 없이 상큼한 복숭아 맛으로 맛있게 먹기 좋음
-체력 보충 및 활력 증진 — 야근이나 피로 시 섭취하면 축 처진 느낌이 줄고 정신이 번쩍 듦</t>
+          <t>고급스러운 패키지 — 네이비와 오렌지 컬러로 깔끔하며 휴대용 용기가 편리함
+편리한 섭취와 달콤함 — 한 번에 섭취하기 쉽고 너무 시지 않아 달콤함
+체력 보충 효과 — 야근이나 피곤할 때 섭취하면 피로 회복에 도움 됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>빠른 피로 해소 — 지속된 피로와 지친 체력을 풀어주고 몸에 힘을 북돋아 줌
-고급스러운 포장 상태 — 포장이 고급스러워 선물용이나 본인 케어용으로 기분 좋게 수령함
-좋은 맛과 높은 만족도 — 비타민 맛이 좋고 부담이 없어 꾸준히 챙겨 먹기 좋음</t>
+          <t>피로 개선 효과 — 섭취 후 피로가 풀리고 컨디션 회복에 도움 됨
+정성스러운 포장 — 고급스럽게 포장되어 선물용으로 전달하기 양호함
+맛있는 비타민 — 비타민 맛이 우수하여 부담 없이 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 복용 — 여러 영양제를 따로 챙길 필요 없이 한 번에 간편하게 섭취 가능함
-알찬 단독 증정 구성 — 카카오 선물하기 전용 구성으로 추가 증정분이 포함되어 실용적임
-컨디션 회복 체감 — 피로감이 줄어들고 컨디션 및 생기 회복에 도움을 줌</t>
+          <t>간편한 올인원 복용 — 여러 영양제 대신 한 번에 챙길 수 있어 간편함
+빠른 피로 회복 — 피로 회복 및 몸의 생기 회복에 도움 됨
+알찬 증정 구성 — 선물하기 전용 추가 증정 구성이 포함되어 실용적임</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 젤리 형태 — 알약 거부감 없이 과일 향의 맛있는 구미 형태로 간식처럼 먹을 수 있음
-쉽고 재미있는 섭취 — 물 없이 하루 2알씩 챙겨 먹기 쉬워 아이와 어른 모두 잘 챙겨 먹게 됨</t>
+          <t>구미 제형의 편의성 — 알약 대신 젤리 형태라 부담 없이 자주 챙겨 먹게 됨
+상큼한 과일 맛 — 새콤달콤한 과일 향으로 맛이 좋아 아이들도 잘 먹음
+꼼꼼한 배송 포장 — 배송 시 포장이 매우 꼼꼼하게 도착함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 포장 — 선물용 패키지가 깔끔하고 예뻐서 주고받을 때 감동을 줌
-목넘김 편한 알약 크기 — 함께 들어있는 알약 크기가 크지 않아 수월하게 삼킬 수 있음
-확실한 컨디션 회복 — 육아나 일상으로 지친 체력을 빠르게 회복시키는 데에 효과적임</t>
+          <t>쉬운 알약 목넘김 — 알약 크기가 작아 액상과 함께 삼키기 용이함
+확실한 컨디션 회복 — 체력이 떨어졌을 때 섭취 시 컨디션 회복에 도움 됨
+이쁜 선물 포장 — 선물 포장 패키지가 고급스럽고 이쁘게 구성됨</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>우수한 컨디션 회복력 — 피로도가 높거나 감기 등 몸이 안 좋을 때 복용 시 빠른 회복에 도움 됨
-편리한 휴대성 및 복용법 — 가지고 다니기 용이하고 마시기 편한 제형으로 섭취가 간편함
-뛰어난 맛과 배송 만족 — 맛이 좋아 부담이 없으며 배송이 빠르고 선물용으로 유용함</t>
+          <t>탁월한 피로 회복 — 복용 후 피로감 감소 및 컨디션 회복에 탁월함
+우수한 휴대성 — 가지고 다니기 좋고 간편하게 마시기 편함
+신속한 배송 서비스 — 주문 후 배송 처리가 신속하여 만족스러움</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 — 용기와 포장이 버리기 아까울 정도로 깔끔하여 선물용으로 제격임
-쓴맛 없는 달콤새콤한 맛 — 홍삼 원료임에도 불구하고 쓴맛이 적고 새콤달콤해서 먹기 편함
-뛰어난 휴대성 — 가방이나 주머니에 간편히 소지하며 챙겨 먹기 적합함</t>
+          <t>높은 브랜드 신뢰도 — 정관장 브랜드로 품질에 대한 믿음이 감
+고급스러운 디자인 — 패키지와 병 디자인이 고급스러워 선물용으로 적합함
+부담 없는 맛 — 쓴맛이 적고 달콤새콤하여 아침저녁으로 먹기 편함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>개운한 피로 개선 — 피로감이 덜하고 섭취 후 하루를 개운하게 보낼 수 있음
-고급스러운 구성 — 선물 패키지가 깔끔하고 증정품 젤리가 포함되어 받으면 기분이 좋음
-맛과 빠른 배송 — 맛이 좋아 먹기 부담 없으며 배송이 빨라 만족스러움</t>
+          <t>고급스러운 패키지 — 패키지 디자인이 고급스럽고 선물용으로 적합함
+피로 개선 체감 — 섭취 시 개운하고 피로감이 덜 느껴짐
+신속한 배송 — 배송이 빠르게 도착하여 이용하기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>지속되는 활력 유지 — 꾸준히 먹으면 피로함이 덜하고 쌩쌩한 상태가 오래 유지됨
-우수한 휴대성과 포장 — 하루 한 개씩 들고 다니기 편하며 성의 있는 정성스러운 포장임</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>뛰어난 휴대성 — 하루 하나씩 가지고 다니며 먹기 편리함
+지속적인 피로 개선 — 꾸준히 섭취 시 피로함이 덜하고 컨디션 유지에 도움 됨
+만족스러운 포장 — 선물 포장 디자인이 깔끔하고 성의 있게 느껴짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4186,15 +4196,14 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 관련 불편 발생 — 배송 기사 연락 문제나 구매 확정 오류 등으로 상품을 미수령하는 상황이 생김</t>
+          <t>배송 미수령 문제 — 구매 결정 과정 중 상품을 실제로 전달받지 못함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>미미한 효과 체감 — 맛있게 먹을 수 있으나 섭취 후 즉각적인 영양 효과 체감은 명확하지 않음
-약간의 씁쓸한 뒷맛 — 달지 않은 편이며 사람에 따라 약간 씁쓸한 맛이 느껴질 수 있음</t>
+          <t>맛에 대한 호불호 — 달지 않고 약간 씁쓸한 느낌이 남아 호불호가 갈림</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
@@ -4203,7 +4212,7 @@
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>큰 알약 크기 — 기존 제품에 비해 알약 크기가 커서 삼키기가 다소 힘들 수 있음</t>
+          <t>큰 알약 크기 — 기존 제품 대비 알약 크기가 커서 삼키기 다소 힘듦</t>
         </is>
       </c>
     </row>
@@ -4522,17 +4531,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 +파로저당단백칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로효소 그린캡슐레이션 증정</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>[라이브 선착순 혜택] "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+앰플 3입 증정</t>
+          <t>'3입 증정' "선물하기 1등 콜라겐" 아일로 타입1 콜라겐 비오틴 앰플 28일분 오간자 에디션+ 앰플 3입 추가 증정</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>[라이브][그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -4557,12 +4566,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
+          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t>아르기닌 증정 남친 활력선물 대한민국 NO.1 김종국 트리플아르기닌 6200 (30포) + 아르기닌 추가 증정</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4619,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>1654</v>
@@ -4634,10 +4643,10 @@
         <v>39</v>
       </c>
       <c r="K19" s="3" t="n">
+        <v>1533</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>248</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>1533</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4648,100 +4657,98 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>과하지 않고 맛있는 풍미 — 달지 않으며 포째 먹거나 물에 타 먹기 좋아 계속 손이 가는 맛임
-풍성한 사은품 혜택 — 포토카드 등 추가 사은품과 예쁜 포장이 제공되어 만족스러움</t>
+          <t>부담 없는 맛 — 많이 달지 않고 맛있어서 그냥 먹거나 물에 타 먹기 편함
+알찬 증정 구성 — 혜자로운 사은품과 포토카드 구성으로 만족도가 높음
+간편한 장 건강 케어 — 맛있고 먹기 편해 일상에서 장 건강 챙기기 용이함</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>식후 더부룩함 해소 — 고기나 밀가루 섭취 후 복용 시 속의 답답함과 더부룩함이 편안해짐
-배변 활동에 도움 — 꾸준히 섭취하면 배변 활동이 원활해지고 속이 개운해짐
-고소한 군고구마 맛 — 군고구마 풍미가 느껴지는 고소한 맛으로 부담 없이 즐기기 좋음</t>
+          <t>소화 개선 효과 — 식후 속 더부룩함이나 답답한 느낌을 줄여줌
+고소한 군고구마 맛 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음
+합리적인 가격 — 할인 행사가 자주 진행되어 가성비 있게 구매 가능함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 오간자 포장 — 은은한 핑크 빛 포장이 매우 고급스럽고 정성스러워 선물하기에 좋음
-피부 상태 개선 체감 — 꾸준히 마시면 피부가 탱탱해지고 맑아지는 느낌을 받음
-간편한 용기와 샘플 구성 — 먹기 편리한 용기 구조에 샘플까지 포함되어 이용이 간편함</t>
+          <t>고급스러운 포장 연출 — 포장이 매우 정성스럽고 예뻐 선물 받는 느낌이 좋음
+피부 상태 개선 체감 — 섭취 후 피부가 탱탱해지고 맑아지는 느낌을 받음
+편리한 섭취 및 샘플 — 먹기 편한 액상 형태이며 샘플 증정이 포함됨</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>저렴한 특가 및 증정 혜택 — 추가 증정 10포와 사은품 구성으로 합리적인 가격에 구매 가능함
-고급스러운 포장과 맛 — 포장이 고급지고 맛도 거부감이 없어 매일 복용하기 적합함</t>
+          <t>저렴한 특가 구매 — 행사 및 추가 증정 포함 저렴한 가격에 구매 가능함
+고급스러운 패키지 — 포장이 고급스럽게 와서 선물용으로 적합함
+무난한 섭취감 — 먹기 편하고 맛도 나쁘지 않아 꾸준히 먹기 좋음</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>부드럽고 다양한 맛 — 퍽퍽하지 않고 부드러우며 소스 종류가 많아 질리지 않고 먹기 좋음
-뛰어난 가성비 패키지 — 많은 수량의 닭가슴살을 부담 없는 저렴한 가격으로 구매 가능함
-간편한 조리 방식 — 전자레인지로 쉽게 조리할 수 있어 다이어트 식단으로 편함</t>
+          <t>부드러운 닭가슴살 식감 — 뻑뻑하지 않고 부드러워 맛있게 먹을 수 있음
+다양한 맛 구성 — 다양한 맛으로 구성되어 매일 먹어도 질리지 않음
+뛰어난 가성비 — 저렴한 가격에 많은 양을 구매할 수 있어 만족스러움</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 텁텁함이나 비린 맛이 없이 달콤하고 깔끔함
-속 편한 저당 음료 — 당과 칼로리가 낮고 복용 후 속 더부룩함이 적어 운동 전후에 적합함
-우수한 포만감과 휴대성 — 슬림한 팩 형태로 휴대가 용이하며 허기를 채워주는 포만감이 있음</t>
+          <t>텁텁함 없는 맛 — 단백질 음료 특유의 비린 맛이나 텁텁함이 거의 없음
+든든한 포만감 — 운동 후나 허기질 때 간식 대용으로 포만감을 줌
+부드러운 목넘김 — 목넘김이 부드럽고 속이 더부룩하지 않아 편안함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>다양한 구성과 맛 — 골라 먹는 재미가 있고 간편식 및 점심 식단으로 활용하기 좋음
-합리적인 세트 가격 — 넉넉한 개수와 증정 보냉백을 포함한 패키지 가격이 가성비가 좋음</t>
+          <t>우수한 가성비 — 저렴한 가격에 알찬 식단 구성으로 구매 가능함
+골라 먹는 재미 — 종류가 다양하여 매일 다채롭게 선택해 먹기 좋음
+사은품 보냉백 증정 — 보냉 파우치가 함께 증정되어 도시락용으로 유용함</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>상큼한 레몬맛 액상 — 부담 없는 레몬맛 액상 타입으로 물에 타서 외출 시 먹기 편리함
-일상 및 운동 활력 증진 — 공복 복용 시 피로 회복과 운동 수행에 도움을 얻을 수 있음</t>
+          <t>상큼한 레몬맛 — 레몬맛 액상 형태라 부담 없이 맛있게 먹기 좋음
+편리한 휴대성 — 스틱 제형이라 외출 시 챙겨 다니기 편리함
+에너지 충전 체감 — 공복이나 운동 전 섭취 시 체력 보충과 활력에 도움 됨</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 — 고함량 아르기닌 함유로 피로 해소와 운동 수행 능력에 효과적임
-선물용 고급 패키지 — 전용 쇼핑백과 추가 포 증정 구성이 잘 갖추어져 선물로 매우 좋음
-간편한 개별 포장 — 1포씩 개별 포장되어 있어 가지고 다니며 하루 1포 챙기기 용이함</t>
+          <t>실속 있는 영양 조합 — 아르기닌과 밀크씨슬을 한 번에 챙길 수 있어 알참
+피로 개선 효과 — 아침에 일어날 때 몸이 덜 무겁고 활력이 생김
+증정 쇼핑백 제공 — 쇼핑백이 함께 포함되어 선물용으로 깔끔함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬을 함께 챙길 수 있어 건강 관리에 효율적임
-확실한 체력 및 피로 개선 — 아침 복용 시 몸이 한결 가볍고 운동 중 활력 유지가 잘 됨
-쇼핑백 포함 선물용 제격 — 고급스러운 쇼핑백이 같이 배송되어 선물 전달용으로도 깔끔함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="60" customHeight="1">
+          <t>고함량 성분 구성 — 1포당 6,200mg 고함량 아르기닌으로 활력 충전에 도움 됨
+간편한 섭취 및 휴대 — 개별 포장되어 원할 때 하나씩 꺼내 먹기 용이함
+고급스러운 포장 — 전용 쇼핑백과 깔끔한 디자인으로 선물하기 좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>탄산수 혼합 시 거품 발생 — 탄산수에 타서 마실 경우 거품이 일어 넘칠 위험이 있어 주의 필요함</t>
-        </is>
-      </c>
+      <c r="C21" s="3" t="inlineStr"/>
       <c r="D21" s="3" t="inlineStr"/>
       <c r="E21" s="3" t="inlineStr"/>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>초기 장 반응 발생 — 복용 초기 뱃속이 꾸르륵거리거나 가스가 차는 현상이 발생할 수 있음
-미배송 문제 발생 — 주문 후 상품을 배송받지 못했다는 불만이 존재함</t>
+          <t>배송 미수령 이슈 — 주문 후 제품을 전달받지 못했다는 의견이 있음</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 해동 발생 — 배송 과정에서 제품이 완전히 녹아 도착하는 경우가 있음</t>
+          <t>배송 중 해동 문제 — 배송 과정에서 제품이 전부 녹아 도착함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 상품 해동 — 상품 수령 시 냉동 상태가 유지되지 못하고 녹아서 옴
-증정품 크기 차이 — 함께 제공되는 사은품 보냉백이 생각보다 다소 크게 느껴질 수 있음</t>
+          <t>제품 해동 상태 — 배송 시 제품이 많이 녹아 도착하는 경우가 있음</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr"/>
@@ -4796,12 +4803,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
+          <t>25,900원</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
           <t>43,900원</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>25,900원</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4998,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4999,54 +5006,58 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=611982831&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911101&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250623/lX1R9GhsEUzz72XUg7VZ611982831_00_00lX1R9GhsEUzz72XUg7VZ.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/BQeSyYNH21gmMrEclYYV610911101_00_01BQeSyYNH21gmMrEclYYV.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1411</v>
+        <v>3</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>작은 알약 사이즈 — 알약 크기가 매우 작아 목넘김이 편하고 섭취가 쉬움</t>
+          <t>뛰어난 가성비 — 다이소 판매 제품으로 가격 대비 품질이 우수함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비 — 약국 제품 대비 가격이 저렴하여 부담 없이 꾸준히 구매하기 좋음</t>
+          <t>접근성 높은 구매 — 올리브영 유통 제품을 다이소에서 쉽게 구매 가능함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>민트 강도 아쉬움 — 스트롱민트임에도 생각보다 청량감이 세지 않음</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5054,49 +5065,49 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911102&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/D3MtLfS4wvzyyoiG4ppT610911102_00_01D3MtLfS4wvzyyoiG4ppT.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2493</v>
+        <v>5</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>무난한 아메리카노 맛 — 일반 커피 맛과 유사하며 타 커피와 섞어 마시기 괜찮음</t>
+          <t>개운한 시원함 — 캡슐을 터트리면 상쾌한 민트 맛이 구강에 남아 개운함</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>포만감 및 배변에 도움 — 음용 시 배가 부르고 물 섭취량이 늘어 화장실 이용에 도음이 됨</t>
+          <t>식후 입가심 용이 — 밥을 먹은 뒤 섭취하면 입안 정돈에 도움 됨</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>물 양 조절 필요 — 물 희석 비율을 제대로 맞추지 않을 경우 다소 역하게 느껴질 수 있음</t>
+          <t>목넘김 및 삼킴 불편 — 캡슐 삼킴 시 거부감이 생겨 버리게 되는 경우 발생함</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
@@ -5105,7 +5116,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5113,12 +5124,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 비타민C 30정</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5128,31 +5139,35 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1060</v>
+        <v>6360</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>속쓰림 없는 편안함 — 비타민C 복용 시 흔한 속쓰림 증상 없이 편안하게 먹을 수 있음</t>
+          <t>뛰어난 가성비 — 저렴한 가격에 부담 없이 구매하기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>피로 개선 및 가성비 — 지친 몸 상태 개선에 도움이 되며 가격이 저렴해 만족함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>믿을 수 있는 브랜드 — 대웅제약 제조 제품이라 안심하고 섭취함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>간편한 일상 섭취 — 매일 하나씩 챙겨 먹기 편하게 구성됨</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -5160,7 +5175,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5168,45 +5183,49 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
+          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>셀트리온</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000135&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/2ijoJLmHVT94XXIOZnda600000135_00_002ijoJLmHVT94XXIOZnda.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3397</v>
+        <v>2498</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>부담 없는 영양 섭취 — 필요한 종합 영양 성분을 착한 가격으로 꾸준하게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>아메리카노 맛 구현 — 일반 아메리카노 맛과 유사하여 커피 대신 마시기 양호함</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>포만감 및 배변 도움 — 물을 많이 마시게 되어 포만감을 주고 화장실 가기 편함</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>미미한 단기 체감 효과 — 복용 초기에는 효과를 직관적으로 체감하기 어려울 수 있음</t>
+          <t>물 조절 미숙 시 비림 — 물 비율을 맞추지 못하면 다소 역한 맛이 느껴질 수 있음</t>
         </is>
       </c>
       <c r="O5" t="inlineStr"/>
@@ -5215,7 +5234,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5223,12 +5242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5238,43 +5257,43 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1216</v>
+        <v>2598</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>상큼한 이온음료 맛 — 포카리스웨트나 이프로 맛이 나 시원하게 음용하기 좋음</t>
+          <t>우수한 가성비 — 가격 부담 없이 지속적으로 구매하여 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>효과적인 수분 보충 — 운동 후나 음주 다음 날 속을 달래고 수분을 빠르게 챙길 수 있음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>외출 시 편리한 휴대성 — 개별 포장되어 가방에 넣고 다니며 타 마시기 편함</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>높은 구매 만족도 — 품질이 양호하여 지속적으로 재구매함</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>가격에 대한 체감 — 일부 구매자 시선에서 다소 비싸게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5282,12 +5301,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>홀베리 유기농 10포 레몬생강즙</t>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>홀베리</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5297,43 +5316,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=965923424&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000145&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260904/TyBV46Gp3x0VYWqJvrvs965923424_00_00TyBV46Gp3x0VYWqJvrvs.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OHEcumxqCcJ047eosRhh600000145_00_00OHEcumxqCcJ047eosRhh.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>509</v>
+        <v>6198</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>염증 완화 및 저렴한 가격 — 몸 염증 완화에 효과가 체감되며 다이소 판매가가 가장 경제적임</t>
+          <t>신뢰도 높은 제조사 — 대웅제약 제품이라 믿고 혈행 개선용으로 섭취함</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>넉넉한 1포 용량 — 한 포당 들어있는 양이 생각보다 많아 만족스러움</t>
+          <t>저렴한 유지 비용 — 가격이 저렴하여 매일 챙겨 먹기 부담 없음</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>강한 쓴맛과 신맛 — 맛이 매우 쓰고 시어서 사람에 따라 복용하기 다소 거북할 수 있음</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5341,50 +5356,62 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
+          <t>동국제약 리포좀 비타민C 30정</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1,500원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253277&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910679&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260422/eIhoZ9JSC5jbp33vSbZX987253277_00_01eIhoZ9JSC5jbp33vSbZX.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250829/3zNHA2Xp859SKsazXUwt610910679_00_003zNHA2Xp859SKsazXUwt.png</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>710</v>
+        <v>1063</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>운동 및 피로 시 활력 충전 — 운동 전에 먹거나 피곤할 때 섭취하면 에너지가 도는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>속쓰림 없는 섭취 — 속쓰림 부작용 없이 편안하게 복용 가능함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>피로 개선 효과 — 지친 상태에서 섭취 시 피로 회복에 도움을 받음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>착한 가격대 — 가성비가 좋아 지속 재구매하기 적합함</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>과대포장 아쉬움 — 약 포장 용기 크기에 비해 내부 공간 여백이 큼</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5392,7 +5419,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
+          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5402,31 +5429,35 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000269&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/LdyaPluhRl2HSeYjB2pX600000269_00_01LdyaPluhRl2HSeYjB2pX.png</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3334</v>
+        <v>478</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>저렴한 가격과 넉넉한 양 — 착한 가격에 양이 넉넉하여 가성비 좋게 지속 복용이 가능함</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>여행용 휴대 편의성 — 소용량 포장이라 여행이나 외출 시 챙겨 가기 편리함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>부드러운 목넘김 — 목넘김이 편하고 가성비가 훌륭함</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -5443,58 +5474,58 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대웅제약 철분 30정 30일분</t>
+          <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>이너뷰 바이 리튠</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000133&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953534&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260820/ahWGJ6KpupAlwxw7p3xm600000133_00_00ahWGJ6KpupAlwxw7p3xm.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/7ii4aNyp1XbM6AH8HjHT994953534_00_007ii4aNyp1XbM6AH8HjHT.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>2318</v>
+        <v>1217</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>변비 부작용 완화 — 철분제 섭취 시 자주 나타나는 변비 증상이 없어 속이 편함</t>
+          <t>이온음료 맛 구현 — 포카리스웨트 및 이프로 맛과 유사해 맛있게 마심</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>착한 가격대 — 가성비가 뛰어나 부담 없이 재구매하기 용이함</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 복용 즉시 효과가 나타나는지 체감하기는 다소 어려움</t>
-        </is>
-      </c>
+          <t>빠른 수분 보충 — 운동 후나 숙취 해소용 수분 보충에 용이함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>개별 포장 휴대성 — 포 형태로 개별 포장되어 들고 다니기 수월함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5502,12 +5533,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>락피도 티니핑 칼슘스틱 12포 12일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>락피도</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5517,37 +5548,37 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953528&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=951817118&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/9Cz26kBHEVc4QcQuToeY994953528_00_009Cz26kBHEVc4QcQuToeY.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260226/jfFr3tgA4ryuIvnhGsc5951817118_00_01jfFr3tgA4ryuIvnhGsc5.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>483</v>
+        <v>326</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>간편한 액상 짜먹는 제형 — 물 없이 액상 형태로 한 포씩 쉽게 짜먹을 수 있어 편함</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>피부 상태 개선 — 꾸준히 복용 시 피부 가려움이 줄고 탄력감 향상에 도움이 됨</t>
-        </is>
-      </c>
+          <t>어린이 선호 캐릭터 — 티니핑 캐릭터 디자인으로 아이들 반응이 좋음</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>아쉬운 단독 복용 맛 — 그냥 짜먹기엔 맛이 약간 아쉬워 물에 타 먹는 번거로움이 있을 수 있음</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>아쉬운 가루 맛 — 가루 부분 맛이 아쉬워 아이들이 거부하기도 함</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>잘 녹지 않는 제형 — 칼슘 가루가 잘 녹지 않아 씹을 때 텁텁함</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5661,52 +5692,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>루테인/눈건강</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>루테인/눈건강</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
         </is>
       </c>
     </row>
@@ -5718,52 +5749,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>셀트리온</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>동국제약</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>이너뷰 바이 리튠</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>홀베리</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>익스트림</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>이너뷰 바이 리튠</t>
+          <t>락피도</t>
         </is>
       </c>
     </row>
@@ -5775,52 +5806,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 토비콤 루테인 지아잔틴 미니 30캡슐</t>
+          <t>[강력한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 스트롱민트 20캡슐 20일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>[산뜻한 상쾌함] [신혜선 PICK] 동국제약 프로폴리스 프레쉬볼 레몬＆민트 20캡슐 20일분</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 비타민C 30정 30일분</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG 오메가3 30캡슐 30일분</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>동국제약 리포좀 비타민C 30정</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 멀티비타민 미네랄 30정 30일분</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약 rTG오메가3 6캡슐 6일분</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>LG생활건강 이너뷰 칼륨밸런스 전해질워터 10포</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>홀베리 유기농 10포 레몬생강즙</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[김종국 PICK] 익스트림 아르기닌 에너지온 2개입 2일분</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>대웅제약 철분 30정 30일분</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 콜라겐 더마스틱 7포</t>
+          <t>락피도 티니핑 칼슘스틱 12포 12일분</t>
         </is>
       </c>
     </row>
@@ -5831,22 +5862,22 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>4.8</v>
@@ -5868,34 +5899,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1411</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2493</v>
+        <v>5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1060</v>
+        <v>6360</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3397</v>
+        <v>2498</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1216</v>
+        <v>2598</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>509</v>
+        <v>6198</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>710</v>
+        <v>1063</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>3334</v>
+        <v>478</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2318</v>
+        <v>1217</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>483</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -5906,97 +5937,106 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>작은 알약 사이즈 — 알약 크기가 매우 작아 목넘김이 편하고 섭취가 쉬움
-뛰어난 가성비 — 약국 제품 대비 가격이 저렴하여 부담 없이 꾸준히 구매하기 좋음</t>
+          <t>뛰어난 가성비 — 다이소 판매 제품으로 가격 대비 품질이 우수함
+접근성 높은 구매 — 올리브영 유통 제품을 다이소에서 쉽게 구매 가능함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>무난한 아메리카노 맛 — 일반 커피 맛과 유사하며 타 커피와 섞어 마시기 괜찮음
-포만감 및 배변에 도움 — 음용 시 배가 부르고 물 섭취량이 늘어 화장실 이용에 도음이 됨</t>
+          <t>개운한 시원함 — 캡슐을 터트리면 상쾌한 민트 맛이 구강에 남아 개운함
+식후 입가심 용이 — 밥을 먹은 뒤 섭취하면 입안 정돈에 도움 됨</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>속쓰림 없는 편안함 — 비타민C 복용 시 흔한 속쓰림 증상 없이 편안하게 먹을 수 있음
-피로 개선 및 가성비 — 지친 몸 상태 개선에 도움이 되며 가격이 저렴해 만족함</t>
+          <t>뛰어난 가성비 — 저렴한 가격에 부담 없이 구매하기 좋음
+믿을 수 있는 브랜드 — 대웅제약 제조 제품이라 안심하고 섭취함
+간편한 일상 섭취 — 매일 하나씩 챙겨 먹기 편하게 구성됨</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 영양 섭취 — 필요한 종합 영양 성분을 착한 가격으로 꾸준하게 챙길 수 있음</t>
+          <t>아메리카노 맛 구현 — 일반 아메리카노 맛과 유사하여 커피 대신 마시기 양호함
+포만감 및 배변 도움 — 물을 많이 마시게 되어 포만감을 주고 화장실 가기 편함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>상큼한 이온음료 맛 — 포카리스웨트나 이프로 맛이 나 시원하게 음용하기 좋음
-효과적인 수분 보충 — 운동 후나 음주 다음 날 속을 달래고 수분을 빠르게 챙길 수 있음
-외출 시 편리한 휴대성 — 개별 포장되어 가방에 넣고 다니며 타 마시기 편함</t>
+          <t>우수한 가성비 — 가격 부담 없이 지속적으로 구매하여 챙겨 먹기 좋음
+높은 구매 만족도 — 품질이 양호하여 지속적으로 재구매함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>염증 완화 및 저렴한 가격 — 몸 염증 완화에 효과가 체감되며 다이소 판매가가 가장 경제적임
-넉넉한 1포 용량 — 한 포당 들어있는 양이 생각보다 많아 만족스러움</t>
+          <t>신뢰도 높은 제조사 — 대웅제약 제품이라 믿고 혈행 개선용으로 섭취함
+저렴한 유지 비용 — 가격이 저렴하여 매일 챙겨 먹기 부담 없음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>운동 및 피로 시 활력 충전 — 운동 전에 먹거나 피곤할 때 섭취하면 에너지가 도는 느낌을 받음</t>
+          <t>속쓰림 없는 섭취 — 속쓰림 부작용 없이 편안하게 복용 가능함
+피로 개선 효과 — 지친 상태에서 섭취 시 피로 회복에 도움을 받음
+착한 가격대 — 가성비가 좋아 지속 재구매하기 적합함</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>저렴한 가격과 넉넉한 양 — 착한 가격에 양이 넉넉하여 가성비 좋게 지속 복용이 가능함</t>
+          <t>여행용 휴대 편의성 — 소용량 포장이라 여행이나 외출 시 챙겨 가기 편리함
+부드러운 목넘김 — 목넘김이 편하고 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>변비 부작용 완화 — 철분제 섭취 시 자주 나타나는 변비 증상이 없어 속이 편함
-착한 가격대 — 가성비가 뛰어나 부담 없이 재구매하기 용이함</t>
+          <t>이온음료 맛 구현 — 포카리스웨트 및 이프로 맛과 유사해 맛있게 마심
+빠른 수분 보충 — 운동 후나 숙취 해소용 수분 보충에 용이함
+개별 포장 휴대성 — 포 형태로 개별 포장되어 들고 다니기 수월함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>간편한 액상 짜먹는 제형 — 물 없이 액상 형태로 한 포씩 쉽게 짜먹을 수 있어 편함
-피부 상태 개선 — 꾸준히 복용 시 피부 가려움이 줄고 탄력감 향상에 도움이 됨</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>어린이 선호 캐릭터 — 티니핑 캐릭터 디자인으로 아이들 반응이 좋음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>민트 강도 아쉬움 — 스트롱민트임에도 생각보다 청량감이 세지 않음</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>물 양 조절 필요 — 물 희석 비율을 제대로 맞추지 않을 경우 다소 역하게 느껴질 수 있음</t>
+          <t>목넘김 및 삼킴 불편 — 캡슐 삼킴 시 거부감이 생겨 버리게 되는 경우 발생함</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr"/>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>미미한 단기 체감 효과 — 복용 초기에는 효과를 직관적으로 체감하기 어려울 수 있음</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>강한 쓴맛과 신맛 — 맛이 매우 쓰고 시어서 사람에 따라 복용하기 다소 거북할 수 있음</t>
-        </is>
-      </c>
-      <c r="I9" s="3" t="inlineStr"/>
+          <t>물 조절 미숙 시 비림 — 물 비율을 맞추지 못하면 다소 역한 맛이 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>가격에 대한 체감 — 일부 구매자 시선에서 다소 비싸게 느껴질 수 있음</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>과대포장 아쉬움 — 약 포장 용기 크기에 비해 내부 공간 여백이 큼</t>
+        </is>
+      </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>효과 체감의 개인차 — 복용 즉시 효과가 나타나는지 체감하기는 다소 어려움</t>
-        </is>
-      </c>
+      <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 단독 복용 맛 — 그냥 짜먹기엔 맛이 약간 아쉬워 물에 타 먹는 번거로움이 있을 수 있음</t>
+          <t>아쉬운 가루 맛 — 가루 부분 맛이 아쉬워 아이들이 거부하기도 함
+잘 녹지 않는 제형 — 칼슘 가루가 잘 녹지 않아 씹을 때 텁텁함</t>
         </is>
       </c>
     </row>
@@ -6008,47 +6048,47 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>2,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>1,500원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>3,000원</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
@@ -6232,7 +6272,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6240,38 +6280,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>레모나 데일리 비타민C 3000 30포 (1개월분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>레모나</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9,400원</t>
+          <t>26,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261031&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026103101ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492946ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>54</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+        <v>25122</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>작은 캡슐 목넘김 — 캡슐 크기가 매우 작고 가벼워 목넘김이 쉬움</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 증정품 구성이 매력적임</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>질 및 장 더블케어 — 질과 장 건강을 한 번에 관리할 수 있어 유용함</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -6279,7 +6331,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6287,50 +6339,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>22064</v>
+        <v>4750</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>우수한 대용량 가성비 — 600정 넉넉한 대용량 수량으로 가격 대비 장기간 복용에 매우 경제적임</t>
+          <t>맛있는 구미 제형 — 간식처럼 씹어 먹을 수 있어 꾸준히 챙기기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>높은 브랜드 신뢰도 — 영국산 원료를 사용하는 검증된 유명 브랜드 제품으로 신뢰감이 큼</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>휴대하기 편한 포장 — 개별 포장이 잘 되어 있어 일상이나 여행 중에도 휴대와 복용이 간편함</t>
-        </is>
-      </c>
+          <t>상큼한 피로 해소 — 상큼한 맛으로 퇴근 후 지쳤을 때 기분 전환에 도움 됨</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
@@ -6346,50 +6394,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>26,000원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492946ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>25115</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 식약처 인정 기능성 원료로 질 건강과 장 건강을 한 번에 케어 가능함</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>초소형 캡슐로 용이한 복용 — 170mg의 매우 작은 캡슐 크기로 목넘김이 막힘없이 매우 수월함</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>귀여운 에디션 굿즈 — 포켓몬 에디션 패키지와 자석 카드케이스 등 굿즈 구성이 유용함</t>
-        </is>
-      </c>
+        <v>8136</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -6397,7 +6433,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6405,46 +6441,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CJ이너비</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10,900원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000264048&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000171584&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026404812ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017158410ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>1011</v>
+        <v>6834</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>귀여운 콜라보 굿즈 — 산리오 마이멜로디 마그넷 액자가 포함되어 구매 만족도가 높음</t>
+          <t>확실한 에너지 충전 — 운동이나 여행 등 에너지가 많이 필요할 때 도움이 됨</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>맛있는 캔디 형태 — 맛이 좋아 간식처럼 거부감 없이 즐겁게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>탄산수 조합 활용 — 액상을 탄산수에 타서 상큼한 에이드처럼 마실 수 있음</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>만족스러운 선물용 — 주변 사람들에게 선물용으로 전달 시 만족도가 높음</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -6452,7 +6492,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6460,45 +6500,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>레모나 데일리 비타민C 3000 30포 (1개월분)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>레모나</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>9,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000261031&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587418ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026103101ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4742</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>상큼하고 쫀득한 젤리 — 레몬라임 맛 등의 쫀득한 구미 타입으로 물 없이 기분 좋게 섭취함</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>합리적인 프로모션 가격 — 세일 기간을 활용하면 가성비 있게 챙겨 먹기 적합함</t>
-        </is>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6507,7 +6539,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6515,45 +6547,37 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>덴프스</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>8133</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2개월분의 넉넉한 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉히 복용할 수 있음</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>만족스러운 사은품 증정 — 구매 시 포토카드 등의 사은품이 동봉되어 소장 가치가 있음</t>
-        </is>
-      </c>
+        <v>15019</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -6562,7 +6586,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6570,34 +6594,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 7일분 택1</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000246058&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024605824ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24290</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>체감되는 장 건강 — 면역력 관리 및 장 건강 개선 효과를 직접 체감함</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>간편한 1일 1캡슐 — 아침 물 한 잔과 함께 복용하기 간편한 제형임</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>알찬 더블 기획 — 더블기획 및 증정품 구성이 알차 가성비가 높음</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6605,7 +6645,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6613,43 +6653,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>에버콜라겐 인앤업비오틴 셀 56정 (28일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>에버콜라겐</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>23,500원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000186592&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018659251ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>474</v>
+        <v>4440</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 이중 케어 — 식약처 인증 원료로 체지방 감소와 장 케어를 동시에 관리 가능함</t>
+          <t>속건조 및 탄력 개선 — 피부 속부터 촘촘하게 채워 탄력 및 보습에 도움 됨</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>상큼한 요거트 맛 — 맛있는 요거트 맛으로 구성되어 매일 한 포씩 질리지 않고 섭취 가능함</t>
+          <t>GPH 콜라겐 원료 — 피부 속 콜라겐과 동일한 구조의 원료를 사용하여 유용함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6660,7 +6700,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6668,43 +6708,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대원제약</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000247884&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024788471ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>5418</v>
+        <v>483</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>수면의 질 개선 효과 — 복용 시 이전보다 수월하고 빠르게 잠에 들 수 있도록 숙면을 도움</t>
+          <t>체지방 및 장 이중케어 — 체지방 감소와 장 건강을 함께 챙길 수 있음</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>안심할 수 있는 식물성 원료 — 식약처 인정 라임과피추출물 100% 식물성 성분을 사용함</t>
+          <t>상큼한 요거트 맛 — 요거트 맛으로 맛있게 하루 한 포씩 먹기 양호함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -6715,7 +6755,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6723,51 +6763,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>53,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000227334&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000193086&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022733451ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0019/A00000019308652ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J11" t="n">
-        <v>9104</v>
+        <v>41073</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>아침 붓기 및 라인 관리 — 야식이나 자극적인 음식 섭취 후 다음 날 붓기를 줄이는 데 효과적임</t>
+          <t>확실한 피로 개선 — 지치고 피곤할 때 섭취 시 컨디션 회복에 탁월함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>물 필요 없는 액상 포 — 작은 액상 스틱 형태로 휴대성이 좋아 언제 어디서나 바로 짜먹음</t>
+          <t>탄산수 음료 활용 — 꾸덕한 액상을 탄산수에 타서 상쾌하게 마시기 편함</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>살짝 감도는 한약 맛 — 상큼한 포도 맛 뒤에 약간의 한약 느낌 풍미가 섞여 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6882,52 +6918,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>멀티비타민/종합비타민</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>프로바이오틱스/유산균</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6939,52 +6975,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
           <t>레모나</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>CJ이너비</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>덴프스</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>에버콜라겐</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
           <t>프로뉴트리션</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>대원제약</t>
-        </is>
-      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>판도라</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -6996,52 +7032,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14입+1입 증정 기획 (2주분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>레모나 데일리 비타민C 3000 30포 (1개월분)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 이너비 브이 캔디 14포 (+마이멜로디 마그넷액자)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
-        </is>
-      </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 7일분 택1</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>에버콜라겐 인앤업비오틴 셀 56정 (28일분)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
           <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[수면 효율증가]대원제약 대원헬스 꿀잠샷 20gX12포 (+2포+수면안대) (14일분)</t>
-        </is>
-      </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>판도라 브이트리티 7/14+1포 (7/15일분)</t>
+          <t>오쏘몰 이뮨 멀티비타민&amp;미네랄 14+1입</t>
         </is>
       </c>
     </row>
@@ -7052,32 +7088,34 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.9</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H6" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="I6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
       <c r="J6" s="3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K6" s="3" t="n">
         <v>4.5</v>
       </c>
-      <c r="K6" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="L6" s="3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="7">
@@ -7087,32 +7125,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
+        <v>25122</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>4750</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>8136</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>6834</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>54</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>22064</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>25115</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1011</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>4742</v>
-      </c>
       <c r="H7" s="3" t="n">
-        <v>8133</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr"/>
+        <v>15019</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>24290</v>
+      </c>
       <c r="J7" s="3" t="n">
-        <v>474</v>
+        <v>4440</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5418</v>
+        <v>483</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>9104</v>
+        <v>41073</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7121,56 +7161,52 @@
           <t>긍정리뷰</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>작은 캡슐 목넘김 — 캡슐 크기가 매우 작고 가벼워 목넘김이 쉬움
+귀여운 콜라보 굿즈 — 포켓몬 에디션 카드케이스 등 증정품 구성이 매력적임
+질 및 장 더블케어 — 질과 장 건강을 한 번에 관리할 수 있어 유용함</t>
+        </is>
+      </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>우수한 대용량 가성비 — 600정 넉넉한 대용량 수량으로 가격 대비 장기간 복용에 매우 경제적임
-높은 브랜드 신뢰도 — 영국산 원료를 사용하는 검증된 유명 브랜드 제품으로 신뢰감이 큼
-휴대하기 편한 포장 — 개별 포장이 잘 되어 있어 일상이나 여행 중에도 휴대와 복용이 간편함</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>질과 장 동시 케어 — 식약처 인정 기능성 원료로 질 건강과 장 건강을 한 번에 케어 가능함
-초소형 캡슐로 용이한 복용 — 170mg의 매우 작은 캡슐 크기로 목넘김이 막힘없이 매우 수월함
-귀여운 에디션 굿즈 — 포켓몬 에디션 패키지와 자석 카드케이스 등 굿즈 구성이 유용함</t>
-        </is>
-      </c>
+          <t>맛있는 구미 제형 — 간식처럼 씹어 먹을 수 있어 꾸준히 챙기기 좋음
+상큼한 피로 해소 — 상큼한 맛으로 퇴근 후 지쳤을 때 기분 전환에 도움 됨</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>귀여운 콜라보 굿즈 — 산리오 마이멜로디 마그넷 액자가 포함되어 구매 만족도가 높음
-맛있는 캔디 형태 — 맛이 좋아 간식처럼 거부감 없이 즐겁게 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>상큼하고 쫀득한 젤리 — 레몬라임 맛 등의 쫀득한 구미 타입으로 물 없이 기분 좋게 섭취함
-합리적인 프로모션 가격 — 세일 기간을 활용하면 가성비 있게 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2개월분의 넉넉한 구성 — 60캡슐 더블 기획으로 두 달 동안 넉넉히 복용할 수 있음
-만족스러운 사은품 증정 — 구매 시 포토카드 등의 사은품이 동봉되어 소장 가치가 있음</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr"/>
+          <t>확실한 에너지 충전 — 운동이나 여행 등 에너지가 많이 필요할 때 도움이 됨
+탄산수 조합 활용 — 액상을 탄산수에 타서 상큼한 에이드처럼 마실 수 있음
+만족스러운 선물용 — 주변 사람들에게 선물용으로 전달 시 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr"/>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>체감되는 장 건강 — 면역력 관리 및 장 건강 개선 효과를 직접 체감함
+간편한 1일 1캡슐 — 아침 물 한 잔과 함께 복용하기 간편한 제형임
+알찬 더블 기획 — 더블기획 및 증정품 구성이 알차 가성비가 높음</t>
+        </is>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>체지방과 장 건강 이중 케어 — 식약처 인증 원료로 체지방 감소와 장 케어를 동시에 관리 가능함
-상큼한 요거트 맛 — 맛있는 요거트 맛으로 구성되어 매일 한 포씩 질리지 않고 섭취 가능함</t>
+          <t>속건조 및 탄력 개선 — 피부 속부터 촘촘하게 채워 탄력 및 보습에 도움 됨
+GPH 콜라겐 원료 — 피부 속 콜라겐과 동일한 구조의 원료를 사용하여 유용함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>수면의 질 개선 효과 — 복용 시 이전보다 수월하고 빠르게 잠에 들 수 있도록 숙면을 도움
-안심할 수 있는 식물성 원료 — 식약처 인정 라임과피추출물 100% 식물성 성분을 사용함</t>
+          <t>체지방 및 장 이중케어 — 체지방 감소와 장 건강을 함께 챙길 수 있음
+상큼한 요거트 맛 — 요거트 맛으로 맛있게 하루 한 포씩 먹기 양호함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>아침 붓기 및 라인 관리 — 야식이나 자극적인 음식 섭취 후 다음 날 붓기를 줄이는 데 효과적임
-물 필요 없는 액상 포 — 작은 액상 스틱 형태로 휴대성이 좋아 언제 어디서나 바로 짜먹음</t>
+          <t>확실한 피로 개선 — 지치고 피곤할 때 섭취 시 컨디션 회복에 탁월함
+탄산수 음료 활용 — 꾸덕한 액상을 탄산수에 타서 상쾌하게 마시기 편함</t>
         </is>
       </c>
     </row>
@@ -7189,11 +7225,7 @@
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>살짝 감도는 한약 맛 — 상큼한 포도 맛 뒤에 약간의 한약 느낌 풍미가 섞여 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="L9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7203,52 +7235,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>26,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>9,200원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>53,900원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
           <t>9,400원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>26,000원</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>9,200원</t>
-        </is>
-      </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>31,400원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>1,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>23,500원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
           <t>39,800원</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>24,700원</t>
+          <t>53,900원</t>
         </is>
       </c>
     </row>
@@ -7374,73 +7406,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" t="n">
         <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -7453,38 +7485,38 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7494,10 +7526,10 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7506,29 +7538,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7538,10 +7570,10 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -7550,7 +7582,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7560,10 +7592,10 @@
         <v>2.5</v>
       </c>
       <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
